--- a/results/canaliculi/542_WT__2_z06c1-2/measurements_euclidean.xlsx
+++ b/results/canaliculi/542_WT__2_z06c1-2/measurements_euclidean.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,16 @@
           <t>assignment_method</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>count_mode</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>preprocess_mode</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -456,91 +466,132 @@
           <t>euclidean</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>tophat</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>v1-raw / pre-validation -- stats below over interior (on_border=False) lacunae only</t>
+          <t>count_mode='edge': one canaliculus = one graph edge (OCY-style); 'path': one canaliculus = one cell-to-tip path (re-counts shared trunks)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>metric</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>median</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>n</t>
+          <t>v1-raw / pre-validation -- stats below over interior (on_border=False) lacunae only</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>canaliculi_count</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>37.6154</v>
-      </c>
-      <c r="C6" t="n">
-        <v>32</v>
-      </c>
-      <c r="D6" t="n">
-        <v>21.5853</v>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>unitless</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>13</v>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>canaliculi_count</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>18.3846</v>
+      </c>
+      <c r="C7" t="n">
+        <v>16</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9.5703</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>total_length_px</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1058.2276</v>
+      </c>
+      <c r="C8" t="n">
+        <v>677.5412</v>
+      </c>
+      <c r="D8" t="n">
+        <v>700.6208</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>mean_canaliculus_length_px</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>157.0446</v>
-      </c>
-      <c r="C7" t="n">
-        <v>147.2442</v>
-      </c>
-      <c r="D7" t="n">
-        <v>60.263</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
+      <c r="B9" t="n">
+        <v>55.0773</v>
+      </c>
+      <c r="C9" t="n">
+        <v>51.0131</v>
+      </c>
+      <c r="D9" t="n">
+        <v>13.1009</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>13</v>
       </c>
     </row>
@@ -595,13 +646,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>2267.6703</v>
+        <v>644.1442</v>
       </c>
       <c r="D2" t="n">
-        <v>133.3924</v>
+        <v>58.5586</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -617,13 +668,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>4395.6908</v>
+        <v>410.8478</v>
       </c>
       <c r="D3" t="n">
-        <v>146.523</v>
+        <v>45.6498</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -639,13 +690,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>1806.2195</v>
+        <v>618.2275</v>
       </c>
       <c r="D4" t="n">
-        <v>95.0642</v>
+        <v>56.2025</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -661,13 +712,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>5461.2737</v>
+        <v>371.9483</v>
       </c>
       <c r="D5" t="n">
-        <v>118.7233</v>
+        <v>41.3276</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -683,13 +734,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>5685.9377</v>
+        <v>561.1442</v>
       </c>
       <c r="D6" t="n">
-        <v>227.4375</v>
+        <v>51.0131</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -705,13 +756,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7" t="n">
-        <v>7577.6273</v>
+        <v>1877.7291</v>
       </c>
       <c r="D7" t="n">
-        <v>210.4896</v>
+        <v>50.7494</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -727,13 +778,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1995.984</v>
+        <v>677.5412</v>
       </c>
       <c r="D8" t="n">
-        <v>90.7265</v>
+        <v>48.3958</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -749,13 +800,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>3491.64</v>
+        <v>626.0732</v>
       </c>
       <c r="D9" t="n">
-        <v>166.2686</v>
+        <v>36.8278</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -771,13 +822,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>12899.4022</v>
+        <v>642.0854</v>
       </c>
       <c r="D10" t="n">
-        <v>204.7524</v>
+        <v>40.1303</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -793,13 +844,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>3059.8805</v>
+        <v>1279.0408</v>
       </c>
       <c r="D11" t="n">
-        <v>95.62130000000001</v>
+        <v>67.31789999999999</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -815,13 +866,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="C12" t="n">
-        <v>27966.6009</v>
+        <v>2732.0693</v>
       </c>
       <c r="D12" t="n">
-        <v>285.3735</v>
+        <v>73.83969999999999</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -837,13 +888,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C13" t="n">
-        <v>5006.304</v>
+        <v>1415.8154</v>
       </c>
       <c r="D13" t="n">
-        <v>147.2442</v>
+        <v>58.9923</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -859,13 +910,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C14" t="n">
-        <v>3505.5395</v>
+        <v>1667.989</v>
       </c>
       <c r="D14" t="n">
-        <v>100.1583</v>
+        <v>72.5213</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -881,13 +932,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>4289.5365</v>
+        <v>876.4478</v>
       </c>
       <c r="D15" t="n">
-        <v>153.1977</v>
+        <v>73.0373</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
@@ -903,13 +954,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>3917.2014</v>
+        <v>753.2691</v>
       </c>
       <c r="D16" t="n">
-        <v>244.8251</v>
+        <v>57.9438</v>
       </c>
       <c r="E16" t="b">
         <v>1</v>
@@ -925,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>9071.2425</v>
+        <v>84.7696</v>
       </c>
       <c r="D17" t="n">
-        <v>201.5832</v>
+        <v>14.1283</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
